--- a/resultados.xlsx
+++ b/resultados.xlsx
@@ -471,38 +471,34 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>-9.81900778771272j</t>
+          <t>-3.6475409836065578j</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>-9.81900778771272j</t>
+          <t>-3.6475409836065578j</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>(8.881784197001252e-16+4.440892098500626e-16j)</t>
+          <t>(-3.1588631531481566+1.82377049180328j)</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>(8.881784197001252e-16+4.440892098500626e-16j)</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>-3.2730025959042406j</t>
-        </is>
+          <t>(3.158863153148158+1.823770491803278j)</t>
+        </is>
+      </c>
+      <c r="E2" t="n">
+        <v>0</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>-3.2730025959042406j</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>-3.2730025959042406j</t>
-        </is>
+          <t>-3.6475409836065578j</t>
+        </is>
+      </c>
+      <c r="G2" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -562,32 +558,32 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>(-1.6653345369377348e-16+0j)</t>
+          <t>0j</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>(-0.15402365157196443-0.8660254037844385j)</t>
+          <t>0j</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>(-0.15402365157196396+0.8660254037844386j)</t>
+          <t>0j</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>(-0.1026824343813095+0j)</t>
+          <t>0j</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>(0.5513412171906547+0j)</t>
+          <t>0j</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>(-0.4486587828093453+0j)</t>
+          <t>0j</t>
         </is>
       </c>
     </row>
@@ -597,17 +593,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>(0.17045737973536218-0.4999999999999999j)</t>
+          <t>(0.0908616817085312-0.052459016393442574j)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>(-0.1704573797353623-0.5j)</t>
+          <t>(-0.0908616817085312-0.052459016393442554j)</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>(2.586636260286008e-16+1j)</t>
+          <t>(1.3236452313887527e-17+0.10491803278688516j)</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -617,12 +613,12 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>(0.5182413917599005-0.29920680703778474j)</t>
+          <t>(0.0908616817085312-0.052459016393442574j)</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>(-0.3477840120245383-0.20079319296221518j)</t>
+          <t>0j</t>
         </is>
       </c>
     </row>
@@ -632,17 +628,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>(0.3488081551325613-0.4999999999999999j)</t>
+          <t>(0.2896216104459435-0.16721311475409836j)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>(-0.3488081551325614-0.4999999999999999j)</t>
+          <t>(-0.2896216104459435-0.16721311475409828j)</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>(2.487631691633148e-16+1j)</t>
+          <t>(3.6553340453591927e-17+0.3344262295081967j)</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -652,12 +648,12 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>(0.6074167794585-0.35069224113066044j)</t>
+          <t>(0.2896216104459435-0.16721311475409836j)</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>(-0.25860862432593873-0.14930775886933947j)</t>
+          <t>0j</t>
         </is>
       </c>
     </row>
@@ -667,17 +663,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>(0.24257282953562168-0.8660254037844386j)</t>
+          <t>(0.42622950819672145+0j)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>(-0.4851456590712433+1.785664799492739e-16j)</t>
+          <t>(-0.21311475409836086-0.3691255819409083j)</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>(0.24257282953562184+0.8660254037844386j)</t>
+          <t>(-0.21311475409836064+0.36912558194090844j)</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -687,12 +683,12 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>(0.3712864147678109-0.6430869345379399j)</t>
+          <t>(0.42622950819672145+0j)</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>(-0.1287135852321892-0.22293846924649877j)</t>
+          <t>0j</t>
         </is>
       </c>
     </row>
@@ -755,17 +751,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>1.7835077539719915j</t>
+          <t>(0.573770491803279+0.9937996436870615j)</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>(-5.551115123125783e-16-1.7835077539719912j)</t>
+          <t>(0.5737704918032788-0.9937996436870615j)</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>(2.220446049250313e-16-4.320714760404071e-16j)</t>
+          <t>(-1.1475409836065582+1.0964554679461481e-16j)</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -775,12 +771,12 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>(0.5148543409287569+0.8917538769859957j)</t>
+          <t>(0.573770491803279+0.9937996436870615j)</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>(-0.5148543409287569+0.8917538769859957j)</t>
+          <t>0j</t>
         </is>
       </c>
     </row>
@@ -792,32 +788,32 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>-5.513412171906548j</t>
+          <t>-2.5j</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>(2.220446049250313e-16+1.2164695702336317j)</t>
+          <t>(-2.165063509461096+1.2500000000000009j)</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>(1.1102230246251565e-15+1.2164695702336317j)</t>
+          <t>(2.165063509461097+1.2499999999999996j)</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>-1.026824343813095j</t>
+          <t>0j</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>-2.2432939140467267j</t>
+          <t>-2.5j</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>-2.2432939140467263j</t>
+          <t>0j</t>
         </is>
       </c>
     </row>
@@ -829,17 +825,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-1.0297086818575136j</t>
+          <t>-1.147540983606557j</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>(6.615562969580741e-16+2.059417363715027j)</t>
+          <t>(-0.9937996436870602+0.5737704918032789j)</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>(-3.3306690738754696e-16-1.029708681857513j)</t>
+          <t>(0.9937996436870605+0.5737704918032783j)</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -849,12 +845,12 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>(-0.8917538769859951-0.5148543409287568j)</t>
+          <t>-1.147540983606557j</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>(0.8917538769859951-0.5148543409287568j)</t>
+          <t>0j</t>
         </is>
       </c>
     </row>
@@ -866,17 +862,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2.0594173637150273j</t>
+          <t>1.1475409836065564j</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>(7.771561172376096e-16-1.0297086818575139j)</t>
+          <t>(0.9937996436870596-0.5737704918032785j)</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>(-1.4432899320127035e-15-1.0297086818575139j)</t>
+          <t>(-0.99379964368706-0.573770491803278j)</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -886,12 +882,12 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>1.0297086818575143j</t>
+          <t>1.1475409836065564j</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>1.029708681857513j</t>
+          <t>0j</t>
         </is>
       </c>
     </row>
@@ -903,17 +899,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>(6.661338147750939e-16+1.7835077539719908j)</t>
+          <t>(0.5737704918032781+0.99379964368706j)</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>-1.7835077539719904j</t>
+          <t>(0.5737704918032779-0.99379964368706j)</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>(-1.3322676295501878e-15-4.875826272716647e-16j)</t>
+          <t>(-1.1475409836065564+1.0964554679461446e-16j)</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -923,12 +919,12 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>(0.514854340928757+0.891753876985996j)</t>
+          <t>(0.5737704918032781+0.99379964368706j)</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>(-0.5148543409287564+0.8917538769859948j)</t>
+          <t>0j</t>
         </is>
       </c>
     </row>
@@ -940,17 +936,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>1.7835077539719955j</t>
+          <t>(0.5737704918032791+0.9937996436870618j)</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>(-6.661338147750939e-16-1.7835077539719952j)</t>
+          <t>(0.5737704918032789-0.9937996436870618j)</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>-4.875826272716652e-16j</t>
+          <t>(-1.1475409836065584+1.0964554679461486e-16j)</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -960,12 +956,12 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>(0.514854340928758+0.8917538769859977j)</t>
+          <t>(0.5737704918032791+0.9937996436870618j)</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>(-0.514854340928758+0.8917538769859977j)</t>
+          <t>0j</t>
         </is>
       </c>
     </row>
@@ -977,17 +973,17 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>1.0297086818575165j</t>
+          <t>1.1475409836065584j</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>(-6.615562969580756e-16-2.0594173637150326j)</t>
+          <t>(0.9937996436870613-0.5737704918032795j)</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>(3.3306690738754696e-16+1.0297086818575159j)</t>
+          <t>(-0.9937996436870618-0.573770491803279j)</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -997,12 +993,12 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>(0.8917538769859976+0.5148543409287583j)</t>
+          <t>1.1475409836065584j</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>(-0.8917538769859976+0.5148543409287583j)</t>
+          <t>0j</t>
         </is>
       </c>
     </row>
@@ -1063,32 +1059,32 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>4.819007787712721j</t>
+          <t>1.1475409836065564j</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>(-4.330127018922192+2.500000000000001j)</t>
+          <t>(0.9937996436870596-0.5737704918032785j)</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>(4.330127018922191+2.4999999999999982j)</t>
+          <t>(-0.99379964368706-0.573770491803278j)</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>3.27300259590424j</t>
+          <t>0j</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>-1.7269974040957585j</t>
+          <t>1.1475409836065564j</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>3.2730025959042397j</t>
+          <t>0j</t>
         </is>
       </c>
     </row>
@@ -1098,17 +1094,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>1.7763568394002505e-15j</t>
+          <t>1.5543122344752192e-15j</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>(-1.5383701491068513e-15-8.881784197001248e-16j)</t>
+          <t>(1.3460738804684943e-15-7.771561172376101e-16j)</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>(1.5383701491068507e-15-8.881784197001258e-16j)</t>
+          <t>(-1.346073880468495e-15-7.771561172376092e-16j)</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1118,12 +1114,12 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>0j</t>
+          <t>1.5543122344752192e-15j</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>1.7763568394002505e-15j</t>
+          <t>0j</t>
         </is>
       </c>
     </row>
@@ -1133,17 +1129,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>3.552713678800501e-15j</t>
+          <t>0j</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>(-3.0767402982137025e-15-1.7763568394002497e-15j)</t>
+          <t>0j</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>(3.0767402982137013e-15-1.7763568394002516e-15j)</t>
+          <t>0j</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1158,7 +1154,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>3.552713678800501e-15j</t>
+          <t>0j</t>
         </is>
       </c>
     </row>
@@ -1168,17 +1164,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>-4.000000000000007j</t>
+          <t>-2.0000000000000018j</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>(-3.4641016151377535+2.000000000000005j)</t>
+          <t>(-1.7320508075688783+1.0000000000000016j)</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>(3.464101615137755+2.0000000000000027j)</t>
+          <t>(1.732050807568879+1.0000000000000004j)</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1188,12 +1184,12 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>-4.0000000000000036j</t>
+          <t>-2.0000000000000018j</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>-3.552713678800501e-15j</t>
+          <t>0j</t>
         </is>
       </c>
     </row>

--- a/resultados.xlsx
+++ b/resultados.xlsx
@@ -471,34 +471,38 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>-3.6475409836065578j</t>
+          <t>-9.81900778771272j</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>-3.6475409836065578j</t>
+          <t>-9.81900778771272j</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>(-3.1588631531481566+1.82377049180328j)</t>
+          <t>(8.881784197001252e-16+4.440892098500626e-16j)</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>(3.158863153148158+1.823770491803278j)</t>
-        </is>
-      </c>
-      <c r="E2" t="n">
-        <v>0</v>
+          <t>(8.881784197001252e-16+4.440892098500626e-16j)</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>-3.2730025959042406j</t>
+        </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>-3.6475409836065578j</t>
-        </is>
-      </c>
-      <c r="G2" t="n">
-        <v>0</v>
+          <t>-3.2730025959042406j</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>-3.2730025959042406j</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -558,32 +562,32 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>0j</t>
+          <t>(-1.6653345369377348e-16+0j)</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>0j</t>
+          <t>(-0.15402365157196443-0.8660254037844385j)</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0j</t>
+          <t>(-0.15402365157196396+0.8660254037844386j)</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>0j</t>
+          <t>(-0.1026824343813095+0j)</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>0j</t>
+          <t>(0.5513412171906547+0j)</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>0j</t>
+          <t>(-0.4486587828093453+0j)</t>
         </is>
       </c>
     </row>
@@ -593,17 +597,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>(0.0908616817085312-0.052459016393442574j)</t>
+          <t>(0.17045737973536218-0.4999999999999999j)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>(-0.0908616817085312-0.052459016393442554j)</t>
+          <t>(-0.1704573797353623-0.5j)</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>(1.3236452313887527e-17+0.10491803278688516j)</t>
+          <t>(2.586636260286008e-16+1j)</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -613,12 +617,12 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>(0.0908616817085312-0.052459016393442574j)</t>
+          <t>(0.5182413917599005-0.29920680703778474j)</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>0j</t>
+          <t>(-0.3477840120245383-0.20079319296221518j)</t>
         </is>
       </c>
     </row>
@@ -628,17 +632,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>(0.2896216104459435-0.16721311475409836j)</t>
+          <t>(0.3488081551325613-0.4999999999999999j)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>(-0.2896216104459435-0.16721311475409828j)</t>
+          <t>(-0.3488081551325614-0.4999999999999999j)</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>(3.6553340453591927e-17+0.3344262295081967j)</t>
+          <t>(2.487631691633148e-16+1j)</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -648,12 +652,12 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>(0.2896216104459435-0.16721311475409836j)</t>
+          <t>(0.6074167794585-0.35069224113066044j)</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>0j</t>
+          <t>(-0.25860862432593873-0.14930775886933947j)</t>
         </is>
       </c>
     </row>
@@ -663,17 +667,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>(0.42622950819672145+0j)</t>
+          <t>(0.4851456590712433+0j)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>(-0.21311475409836086-0.3691255819409083j)</t>
+          <t>(-0.24257282953562193-0.8660254037844384j)</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>(-0.21311475409836064+0.36912558194090844j)</t>
+          <t>(-0.2425728295356214+0.8660254037844386j)</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -683,12 +687,12 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>(0.42622950819672145+0j)</t>
+          <t>(0.7425728295356216+0j)</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>0j</t>
+          <t>(-0.25742717046437835+0j)</t>
         </is>
       </c>
     </row>
@@ -751,17 +755,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>(0.573770491803279+0.9937996436870615j)</t>
+          <t>1.7835077539719915j</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>(0.5737704918032788-0.9937996436870615j)</t>
+          <t>(-5.551115123125783e-16-1.7835077539719912j)</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>(-1.1475409836065582+1.0964554679461481e-16j)</t>
+          <t>(2.220446049250313e-16-4.320714760404071e-16j)</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -771,12 +775,12 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>(0.573770491803279+0.9937996436870615j)</t>
+          <t>(0.5148543409287569+0.8917538769859957j)</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>0j</t>
+          <t>(-0.5148543409287569+0.8917538769859957j)</t>
         </is>
       </c>
     </row>
@@ -788,32 +792,32 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>-2.5j</t>
+          <t>-5.513412171906548j</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>(-2.165063509461096+1.2500000000000009j)</t>
+          <t>(2.220446049250313e-16+1.2164695702336317j)</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>(2.165063509461097+1.2499999999999996j)</t>
+          <t>(1.1102230246251565e-15+1.2164695702336317j)</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0j</t>
+          <t>-1.026824343813095j</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>-2.5j</t>
+          <t>-2.2432939140467267j</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>0j</t>
+          <t>-2.2432939140467263j</t>
         </is>
       </c>
     </row>
@@ -825,17 +829,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-1.147540983606557j</t>
+          <t>-2.059417363715027j</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>(-0.9937996436870602+0.5737704918032789j)</t>
+          <t>(3.3306690738754696e-16+1.0297086818575134j)</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>(0.9937996436870605+0.5737704918032783j)</t>
+          <t>(3.3306690738754696e-16+1.0297086818575134j)</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -845,12 +849,12 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>-1.147540983606557j</t>
+          <t>-1.0297086818575134j</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>0j</t>
+          <t>-1.0297086818575134j</t>
         </is>
       </c>
     </row>
@@ -862,17 +866,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>1.1475409836065564j</t>
+          <t>2.0594173637150273j</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>(0.9937996436870596-0.5737704918032785j)</t>
+          <t>(7.771561172376096e-16-1.0297086818575139j)</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>(-0.99379964368706-0.573770491803278j)</t>
+          <t>(-1.4432899320127035e-15-1.0297086818575139j)</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -882,12 +886,12 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>1.1475409836065564j</t>
+          <t>1.0297086818575143j</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>0j</t>
+          <t>1.029708681857513j</t>
         </is>
       </c>
     </row>
@@ -899,17 +903,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>(0.5737704918032781+0.99379964368706j)</t>
+          <t>(6.661338147750939e-16+1.7835077539719908j)</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>(0.5737704918032779-0.99379964368706j)</t>
+          <t>-1.7835077539719904j</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>(-1.1475409836065564+1.0964554679461446e-16j)</t>
+          <t>(-1.3322676295501878e-15-4.875826272716647e-16j)</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -919,12 +923,12 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>(0.5737704918032781+0.99379964368706j)</t>
+          <t>(0.514854340928757+0.891753876985996j)</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>0j</t>
+          <t>(-0.5148543409287564+0.8917538769859948j)</t>
         </is>
       </c>
     </row>
@@ -936,17 +940,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>(0.5737704918032791+0.9937996436870618j)</t>
+          <t>1.7835077539719955j</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>(0.5737704918032789-0.9937996436870618j)</t>
+          <t>(-6.661338147750939e-16-1.7835077539719952j)</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>(-1.1475409836065584+1.0964554679461486e-16j)</t>
+          <t>-4.875826272716652e-16j</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -956,12 +960,12 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>(0.5737704918032791+0.9937996436870618j)</t>
+          <t>(0.514854340928758+0.8917538769859977j)</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>0j</t>
+          <t>(-0.514854340928758+0.8917538769859977j)</t>
         </is>
       </c>
     </row>
@@ -973,17 +977,17 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>1.1475409836065584j</t>
+          <t>2.0594173637150326j</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>(0.9937996436870613-0.5737704918032795j)</t>
+          <t>(-3.3306690738754696e-16-1.0297086818575165j)</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>(-0.9937996436870618-0.573770491803279j)</t>
+          <t>(-3.3306690738754696e-16-1.0297086818575165j)</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -993,12 +997,12 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>1.1475409836065584j</t>
+          <t>1.0297086818575163j</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>0j</t>
+          <t>1.0297086818575163j</t>
         </is>
       </c>
     </row>
@@ -1059,32 +1063,32 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>1.1475409836065564j</t>
+          <t>4.819007787712721j</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>(0.9937996436870596-0.5737704918032785j)</t>
+          <t>(-4.330127018922192+2.500000000000001j)</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>(-0.99379964368706-0.573770491803278j)</t>
+          <t>(4.330127018922191+2.4999999999999982j)</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>0j</t>
+          <t>3.27300259590424j</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>1.1475409836065564j</t>
+          <t>-1.7269974040957585j</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>0j</t>
+          <t>3.2730025959042397j</t>
         </is>
       </c>
     </row>
@@ -1094,17 +1098,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>1.5543122344752192e-15j</t>
+          <t>1.7763568394002505e-15j</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>(1.3460738804684943e-15-7.771561172376101e-16j)</t>
+          <t>(-1.5383701491068513e-15-8.881784197001248e-16j)</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>(-1.346073880468495e-15-7.771561172376092e-16j)</t>
+          <t>(1.5383701491068507e-15-8.881784197001258e-16j)</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1114,12 +1118,12 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>1.5543122344752192e-15j</t>
+          <t>0j</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>0j</t>
+          <t>1.7763568394002505e-15j</t>
         </is>
       </c>
     </row>
@@ -1129,17 +1133,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>0j</t>
+          <t>3.552713678800501e-15j</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>0j</t>
+          <t>(-3.0767402982137025e-15-1.7763568394002497e-15j)</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>0j</t>
+          <t>(3.0767402982137013e-15-1.7763568394002516e-15j)</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1154,7 +1158,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>0j</t>
+          <t>3.552713678800501e-15j</t>
         </is>
       </c>
     </row>
@@ -1164,17 +1168,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>-2.0000000000000018j</t>
+          <t>-4.000000000000007j</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>(-1.7320508075688783+1.0000000000000016j)</t>
+          <t>(-3.4641016151377535+2.000000000000005j)</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>(1.732050807568879+1.0000000000000004j)</t>
+          <t>(3.464101615137755+2.0000000000000027j)</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1184,12 +1188,12 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>-2.0000000000000018j</t>
+          <t>-4.0000000000000036j</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>0j</t>
+          <t>-3.552713678800501e-15j</t>
         </is>
       </c>
     </row>

--- a/resultados.xlsx
+++ b/resultados.xlsx
@@ -471,37 +471,37 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>-9.81900778771272j</t>
+          <t>8.0180 ∠ -90.00°</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>-9.81900778771272j</t>
+          <t>8.0180 ∠ -90.00°</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>(8.881784197001252e-16+4.440892098500626e-16j)</t>
+          <t>0.0000 ∠ 0.00°</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>(8.881784197001252e-16+4.440892098500626e-16j)</t>
+          <t>0.0000 ∠ 0.00°</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>-3.2730025959042406j</t>
+          <t>2.6727 ∠ -90.00°</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>-3.2730025959042406j</t>
+          <t>2.6727 ∠ -90.00°</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>-3.2730025959042406j</t>
+          <t>2.6727 ∠ -90.00°</t>
         </is>
       </c>
     </row>
@@ -557,142 +557,150 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="n">
-        <v>1</v>
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>(-1.6653345369377348e-16+0j)</t>
+          <t>0.0000 ∠ 0.00°</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>(-0.15402365157196443-0.8660254037844385j)</t>
+          <t>0.9543 ∠ -114.84°</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>(-0.15402365157196396+0.8660254037844386j)</t>
+          <t>0.9543 ∠ 114.84°</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>(-0.1026824343813095+0j)</t>
+          <t>0.2673 ∠ 180.00°</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>(0.5513412171906547+0j)</t>
+          <t>0.6336 ∠ 0.00°</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>(-0.4486587828093453+0j)</t>
+          <t>0.3664 ∠ 180.00°</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="n">
-        <v>2</v>
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>(0.17045737973536218-0.4999999999999999j)</t>
+          <t>0.5821 ∠ -59.20°</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>(-0.1704573797353623-0.5j)</t>
+          <t>0.5821 ∠ -120.80°</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>(2.586636260286008e-16+1j)</t>
+          <t>1.0000 ∠ 90.00°</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0j</t>
+          <t>0.0000 ∠ 0.00°</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>(0.5182413917599005-0.29920680703778474j)</t>
+          <t>0.6721 ∠ -30.00°</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>(-0.3477840120245383-0.20079319296221518j)</t>
+          <t>0.3279 ∠ -150.00°</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="n">
-        <v>3</v>
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>(0.3488081551325613-0.4999999999999999j)</t>
+          <t>0.6685 ∠ -48.42°</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>(-0.3488081551325614-0.4999999999999999j)</t>
+          <t>0.6685 ∠ -131.58°</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>(2.487631691633148e-16+1j)</t>
+          <t>1.0000 ∠ 90.00°</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0j</t>
+          <t>0.0000 ∠ 0.00°</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>(0.6074167794585-0.35069224113066044j)</t>
+          <t>0.7562 ∠ -30.00°</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>(-0.25860862432593873-0.14930775886933947j)</t>
+          <t>0.2438 ∠ -150.00°</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="n">
-        <v>4</v>
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>(0.4851456590712433+0j)</t>
+          <t>0.5796 ∠ 0.00°</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>(-0.24257282953562193-0.8660254037844384j)</t>
+          <t>0.9132 ∠ -108.50°</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>(-0.2425728295356214+0.8660254037844386j)</t>
+          <t>0.9132 ∠ 108.50°</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0j</t>
+          <t>0.0000 ∠ 0.00°</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>(0.7425728295356216+0j)</t>
+          <t>0.7898 ∠ 0.00°</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>(-0.25742717046437835+0j)</t>
+          <t>0.2102 ∠ 180.00°</t>
         </is>
       </c>
     </row>
@@ -755,32 +763,32 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>1.7835077539719915j</t>
+          <t>1.4564 ∠ 90.00°</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>(-5.551115123125783e-16-1.7835077539719912j)</t>
+          <t>1.4564 ∠ -90.00°</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>(2.220446049250313e-16-4.320714760404071e-16j)</t>
+          <t>0.0000 ∠ 0.00°</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>0j</t>
+          <t>0.0000 ∠ 0.00°</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>(0.5148543409287569+0.8917538769859957j)</t>
+          <t>0.8408 ∠ 60.00°</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>(-0.5148543409287569+0.8917538769859957j)</t>
+          <t>0.8408 ∠ 120.00°</t>
         </is>
       </c>
     </row>
@@ -792,32 +800,32 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>-5.513412171906548j</t>
+          <t>6.3363 ∠ -90.00°</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>(2.220446049250313e-16+1.2164695702336317j)</t>
+          <t>0.8408 ∠ -90.00°</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>(1.1102230246251565e-15+1.2164695702336317j)</t>
+          <t>0.8408 ∠ -90.00°</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>-1.026824343813095j</t>
+          <t>2.6727 ∠ -90.00°</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>-2.2432939140467267j</t>
+          <t>1.8318 ∠ -90.00°</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>-2.2432939140467263j</t>
+          <t>1.8318 ∠ -90.00°</t>
         </is>
       </c>
     </row>
@@ -829,32 +837,32 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-2.059417363715027j</t>
+          <t>1.6817 ∠ -90.00°</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>(3.3306690738754696e-16+1.0297086818575134j)</t>
+          <t>0.8408 ∠ 90.00°</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>(3.3306690738754696e-16+1.0297086818575134j)</t>
+          <t>0.8408 ∠ 90.00°</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0j</t>
+          <t>0.0000 ∠ 0.00°</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>-1.0297086818575134j</t>
+          <t>0.8408 ∠ -90.00°</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>-1.0297086818575134j</t>
+          <t>0.8408 ∠ -90.00°</t>
         </is>
       </c>
     </row>
@@ -866,32 +874,32 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2.0594173637150273j</t>
+          <t>1.6817 ∠ 90.00°</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>(7.771561172376096e-16-1.0297086818575139j)</t>
+          <t>0.8408 ∠ -90.00°</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>(-1.4432899320127035e-15-1.0297086818575139j)</t>
+          <t>0.8408 ∠ -90.00°</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0j</t>
+          <t>0.0000 ∠ 0.00°</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>1.0297086818575143j</t>
+          <t>0.8408 ∠ 90.00°</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>1.029708681857513j</t>
+          <t>0.8408 ∠ 90.00°</t>
         </is>
       </c>
     </row>
@@ -903,32 +911,32 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>(6.661338147750939e-16+1.7835077539719908j)</t>
+          <t>1.4564 ∠ 90.00°</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>-1.7835077539719904j</t>
+          <t>1.4564 ∠ -90.00°</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>(-1.3322676295501878e-15-4.875826272716647e-16j)</t>
+          <t>0.0000 ∠ 0.00°</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0j</t>
+          <t>0.0000 ∠ 0.00°</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>(0.514854340928757+0.891753876985996j)</t>
+          <t>0.8408 ∠ 60.00°</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>(-0.5148543409287564+0.8917538769859948j)</t>
+          <t>0.8408 ∠ 120.00°</t>
         </is>
       </c>
     </row>
@@ -940,32 +948,32 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>1.7835077539719955j</t>
+          <t>1.4564 ∠ 90.00°</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>(-6.661338147750939e-16-1.7835077539719952j)</t>
+          <t>1.4564 ∠ -90.00°</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>-4.875826272716652e-16j</t>
+          <t>0.0000 ∠ 0.00°</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0j</t>
+          <t>0.0000 ∠ 0.00°</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>(0.514854340928758+0.8917538769859977j)</t>
+          <t>0.8408 ∠ 60.00°</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>(-0.514854340928758+0.8917538769859977j)</t>
+          <t>0.8408 ∠ 120.00°</t>
         </is>
       </c>
     </row>
@@ -977,32 +985,32 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2.0594173637150326j</t>
+          <t>1.6817 ∠ 90.00°</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>(-3.3306690738754696e-16-1.0297086818575165j)</t>
+          <t>0.8408 ∠ -90.00°</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>(-3.3306690738754696e-16-1.0297086818575165j)</t>
+          <t>0.8408 ∠ -90.00°</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0j</t>
+          <t>0.0000 ∠ 0.00°</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>1.0297086818575163j</t>
+          <t>0.8408 ∠ 90.00°</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>1.0297086818575163j</t>
+          <t>0.8408 ∠ 90.00°</t>
         </is>
       </c>
     </row>
@@ -1058,142 +1066,150 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="n">
-        <v>1</v>
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>4.819007787712721j</t>
+          <t>3.0180 ∠ 90.00°</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>(-4.330127018922192+2.500000000000001j)</t>
+          <t>5.0000 ∠ 150.00°</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>(4.330127018922191+2.4999999999999982j)</t>
+          <t>5.0000 ∠ 30.00°</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>3.27300259590424j</t>
+          <t>2.6727 ∠ 90.00°</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>-1.7269974040957585j</t>
+          <t>2.3273 ∠ -90.00°</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>3.2730025959042397j</t>
+          <t>2.6727 ∠ 90.00°</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="n">
-        <v>2</v>
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>1.7763568394002505e-15j</t>
+          <t>0.0000 ∠ 0.00°</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>(-1.5383701491068513e-15-8.881784197001248e-16j)</t>
+          <t>0.0000 ∠ 0.00°</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>(1.5383701491068507e-15-8.881784197001258e-16j)</t>
+          <t>0.0000 ∠ 0.00°</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0j</t>
+          <t>0.0000 ∠ 0.00°</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>0j</t>
+          <t>0.0000 ∠ 0.00°</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>1.7763568394002505e-15j</t>
+          <t>0.0000 ∠ 0.00°</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="n">
-        <v>3</v>
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>3.552713678800501e-15j</t>
+          <t>0.0000 ∠ 0.00°</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>(-3.0767402982137025e-15-1.7763568394002497e-15j)</t>
+          <t>0.0000 ∠ 0.00°</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>(3.0767402982137013e-15-1.7763568394002516e-15j)</t>
+          <t>0.0000 ∠ 0.00°</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0j</t>
+          <t>0.0000 ∠ 0.00°</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>0j</t>
+          <t>0.0000 ∠ 0.00°</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>3.552713678800501e-15j</t>
+          <t>0.0000 ∠ 0.00°</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="n">
-        <v>4</v>
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>-4.000000000000007j</t>
+          <t>4.0000 ∠ -90.00°</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>(-3.4641016151377535+2.000000000000005j)</t>
+          <t>4.0000 ∠ 150.00°</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>(3.464101615137755+2.0000000000000027j)</t>
+          <t>4.0000 ∠ 30.00°</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0j</t>
+          <t>0.0000 ∠ 0.00°</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>-4.0000000000000036j</t>
+          <t>4.0000 ∠ -90.00°</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>-3.552713678800501e-15j</t>
+          <t>0.0000 ∠ 0.00°</t>
         </is>
       </c>
     </row>

--- a/resultados.xlsx
+++ b/resultados.xlsx
@@ -7,10 +7,13 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Correntes de Falta" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Tensões nas Barras" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Correntes de Contribuição" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Correntes Injetadas" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Ybarra (+) (-)" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Zbarra (+) (-)" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Ybarra (0)" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Zbarra (0)" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Curto Monofásico - Barra 1" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Curto Trifásico - Barra 4" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Curto Bifásico-Terra - Barra 2" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -428,80 +431,120 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G2"/>
+  <dimension ref="A1:E5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>IF</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Fase A</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Fase B</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>Fase C</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>Seq. (0)</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>Seq. (+)</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>Seq. (-)</t>
-        </is>
+      <c r="B1" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>32.5656 ∠ -90.00°</t>
-        </is>
+      <c r="A2" s="1" t="n">
+        <v>1</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>32.5656 ∠ -90.00°</t>
+          <t>-26.875j</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>0.0000 ∠ 0.00°</t>
+          <t>21.875j</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.0000 ∠ 0.00°</t>
+          <t>0j</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>10.8552 ∠ -90.00°</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>10.8552 ∠ -90.00°</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>10.8552 ∠ -90.00°</t>
+          <t>0j</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>21.875j</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>-31.875j</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>10j</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>0j</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>0j</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>10j</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>-35j</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>25j</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>0j</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>0j</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>25j</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>-29j</t>
         </is>
       </c>
     </row>
@@ -516,191 +559,120 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G5"/>
+  <dimension ref="A1:E5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Barra</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Fase A</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Fase B</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>Fase C</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>Seq. (0)</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>Seq. (+)</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>Seq. (-)</t>
-        </is>
+      <c r="B1" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="A2" s="1" t="n">
+        <v>1</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>0.0000 ∠ 0.00°</t>
+          <t>0.13707865168539324j</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>8.0579 ∠ -111.45°</t>
+          <t>0.12269662921348315j</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>8.0579 ∠ 111.45°</t>
+          <t>0.09123595505617976j</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>1.9642 ∠ 180.00°</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>5.3122 ∠ 0.00°</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>3.3480 ∠ 180.00°</t>
+          <t>0.0786516853932584j</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="A3" s="1" t="n">
+        <v>2</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>21.1867 ∠ 0.00°</t>
+          <t>0.12269662921348314j</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>186.4700 ∠ -112.32°</t>
+          <t>0.15074157303370786j</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>186.4700 ∠ 112.32°</t>
+          <t>0.11208988764044941j</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>40.1479 ∠ 180.00°</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>130.2602 ∠ 0.00°</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>68.9256 ∠ 180.00°</t>
+          <t>0.09662921348314603j</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="A4" s="1" t="n">
+        <v>3</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>78.5320 ∠ 0.00°</t>
+          <t>0.09123595505617975j</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>184.8705 ∠ -111.08°</t>
+          <t>0.1120898876404494j</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>184.8705 ∠ 111.08°</t>
+          <t>0.15770786516853927j</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>18.1491 ∠ 180.00°</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>147.9335 ∠ 0.00°</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>51.2524 ∠ 180.00°</t>
+          <t>0.1359550561797752j</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="A5" s="1" t="n">
+        <v>4</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>4.2205 ∠ 0.00°</t>
+          <t>0.0786516853932584j</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>8.0803 ∠ -111.85°</t>
+          <t>0.09662921348314603j</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>8.0803 ∠ 111.85°</t>
+          <t>0.1359550561797752j</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0.5978 ∠ 180.00°</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>6.7393 ∠ 0.00°</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>1.9210 ∠ 180.00°</t>
+          <t>0.1516853932584269j</t>
         </is>
       </c>
     </row>
@@ -715,302 +687,120 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G8"/>
+  <dimension ref="A1:E5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Nome</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Fase A</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Fase B</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>Fase C</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>Seq. (0)</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>Seq. (+)</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>Seq. (-)</t>
-        </is>
+      <c r="B1" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Linha 2-3</t>
-        </is>
+      <c r="A2" s="1" t="n">
+        <v>1</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>0.3894 ∠ 90.00°</t>
+          <t>-31.875j</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>0.0561 ∠ -90.00°</t>
+          <t>21.875j</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.0561 ∠ -90.00°</t>
+          <t>0j</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>0.0924 ∠ 90.00°</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>0.1485 ∠ 90.00°</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>0.1485 ∠ 90.00°</t>
+          <t>0j</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>G1</t>
-        </is>
+      <c r="A3" s="1" t="n">
+        <v>2</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>23.6099 ∠ -90.00°</t>
+          <t>21.875j</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>1.2896 ∠ -90.00°</t>
+          <t>-26.875j</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1.2896 ∠ -90.00°</t>
+          <t>5j</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>8.7297 ∠ -90.00°</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>7.4401 ∠ -90.00°</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>7.4401 ∠ -90.00°</t>
+          <t>0j</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>G4</t>
-        </is>
+      <c r="A4" s="1" t="n">
+        <v>3</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>8.9557 ∠ -90.00°</t>
+          <t>0j</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>1.2896 ∠ 90.00°</t>
+          <t>5j</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>1.2896 ∠ 90.00°</t>
+          <t>-30j</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2.1255 ∠ -90.00°</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>3.4151 ∠ -90.00°</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>3.4151 ∠ -90.00°</t>
+          <t>25j</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Trafo 1 (Primário)</t>
-        </is>
+      <c r="A5" s="1" t="n">
+        <v>4</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>8.9557 ∠ 90.00°</t>
+          <t>0j</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>1.2896 ∠ -90.00°</t>
+          <t>0j</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>1.2896 ∠ -90.00°</t>
+          <t>25j</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2.1255 ∠ 90.00°</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>3.4151 ∠ 90.00°</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>3.4151 ∠ 90.00°</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Trafo 1 (Secundário)</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>0.3894 ∠ 90.00°</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>0.0561 ∠ -90.00°</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>0.0561 ∠ -90.00°</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>0.0924 ∠ 90.00°</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>0.1485 ∠ 90.00°</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>0.1485 ∠ 90.00°</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Trafo 2 (Primário)</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>0.3894 ∠ 90.00°</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>0.0561 ∠ -90.00°</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>0.0561 ∠ -90.00°</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>0.0924 ∠ 90.00°</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>0.1485 ∠ 90.00°</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>0.1485 ∠ 90.00°</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Trafo 2 (Secundário)</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>8.9557 ∠ 90.00°</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>1.2896 ∠ -90.00°</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>1.2896 ∠ -90.00°</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>2.1255 ∠ 90.00°</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>3.4151 ∠ 90.00°</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>3.4151 ∠ 90.00°</t>
+          <t>-33j</t>
         </is>
       </c>
     </row>
@@ -1025,41 +815,174 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G5"/>
+  <dimension ref="A1:E5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="B1" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>0.08041958041958042j</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>0.07146853146853147j</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>0.032307692307692294j</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>0.02447552447552447j</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>0.07146853146853147j</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>0.10413986013986012j</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>0.047076923076923065j</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>0.035664335664335654j</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>0.0323076923076923j</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>0.047076923076923065j</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>0.11169230769230767j</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>0.08461538461538459j</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>0.02447552447552447j</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>0.035664335664335654j</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>0.08461538461538459j</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>0.09440559440559439j</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Barra</t>
+          <t>Tipo</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
+          <t>Elemento / IF</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
           <t>Fase A</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Fase B</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Fase C</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Seq. (0)</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Seq. (+)</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Seq. (-)</t>
         </is>
@@ -1068,49 +991,54 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>Correntes de Falta</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>13.3206 ∠ 90.00°</t>
+          <t>32.5656 ∠ -90.00°</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>19.2450 ∠ 150.00°</t>
+          <t>32.5656 ∠ -90.00°</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>19.2450 ∠ 30.00°</t>
+          <t>0.0000 ∠ 0.00°</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>10.8552 ∠ 90.00°</t>
+          <t>0.0000 ∠ 0.00°</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>8.3898 ∠ -90.00°</t>
+          <t>10.8552 ∠ -90.00°</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>10.8552 ∠ 90.00°</t>
+          <t>10.8552 ∠ -90.00°</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>10.8552 ∠ -90.00°</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>Tensões nas Barras</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>0.0000 ∠ 0.00°</t>
+          <t>Barra 1</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -1120,94 +1048,2069 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>0.0000 ∠ 0.00°</t>
+          <t>8.0579 ∠ -111.45°</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0.0000 ∠ 0.00°</t>
+          <t>8.0579 ∠ 111.45°</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>0.0000 ∠ 0.00°</t>
+          <t>1.9642 ∠ 180.00°</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>0.0000 ∠ 0.00°</t>
+          <t>5.3122 ∠ 0.00°</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>3.3480 ∠ 180.00°</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>Tensões nas Barras</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>0.0000 ∠ 0.00°</t>
+          <t>Barra 2</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>0.0000 ∠ 0.00°</t>
+          <t>21.1867 ∠ 0.00°</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>0.0000 ∠ 0.00°</t>
+          <t>186.4700 ∠ -112.32°</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0.0000 ∠ 0.00°</t>
+          <t>186.4700 ∠ 112.32°</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>0.0000 ∠ 0.00°</t>
+          <t>40.1479 ∠ 180.00°</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>0.0000 ∠ 0.00°</t>
+          <t>130.2602 ∠ 0.00°</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>68.9256 ∠ 180.00°</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>Tensões nas Barras</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
+          <t>Barra 3</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>78.5320 ∠ 0.00°</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>184.8705 ∠ -111.08°</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>184.8705 ∠ 111.08°</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>18.1491 ∠ 180.00°</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>147.9335 ∠ 0.00°</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>51.2524 ∠ 180.00°</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Tensões nas Barras</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Barra 4</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>4.2205 ∠ 0.00°</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>8.0803 ∠ -111.85°</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>8.0803 ∠ 111.85°</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>0.5978 ∠ 180.00°</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>6.7393 ∠ 0.00°</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>1.9210 ∠ 180.00°</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Correntes de Contribuição</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Linha 2-3</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>0.3894 ∠ 90.00°</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>0.0561 ∠ -90.00°</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>0.0561 ∠ -90.00°</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>0.0924 ∠ 90.00°</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>0.1485 ∠ 90.00°</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>0.1485 ∠ 90.00°</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Correntes de Contribuição</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>G1</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>23.6099 ∠ -90.00°</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>1.2896 ∠ -90.00°</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>1.2896 ∠ -90.00°</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>8.7297 ∠ -90.00°</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>7.4401 ∠ -90.00°</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>7.4401 ∠ -90.00°</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Correntes de Contribuição</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>G4</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>8.9557 ∠ -90.00°</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>1.2896 ∠ 90.00°</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>1.2896 ∠ 90.00°</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>2.1255 ∠ -90.00°</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>3.4151 ∠ -90.00°</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>3.4151 ∠ -90.00°</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Correntes de Contribuição</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Trafo 1 (Primário)</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>8.9557 ∠ 90.00°</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>1.2896 ∠ -90.00°</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>1.2896 ∠ -90.00°</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>2.1255 ∠ 90.00°</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>3.4151 ∠ 90.00°</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>3.4151 ∠ 90.00°</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Correntes de Contribuição</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Trafo 1 (Secundário)</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>0.3894 ∠ 90.00°</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>0.0561 ∠ -90.00°</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>0.0561 ∠ -90.00°</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>0.0924 ∠ 90.00°</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>0.1485 ∠ 90.00°</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>0.1485 ∠ 90.00°</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Correntes de Contribuição</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Trafo 2 (Primário)</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>0.3894 ∠ 90.00°</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>0.0561 ∠ -90.00°</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>0.0561 ∠ -90.00°</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>0.0924 ∠ 90.00°</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>0.1485 ∠ 90.00°</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>0.1485 ∠ 90.00°</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Correntes de Contribuição</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Trafo 2 (Secundário)</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>8.9557 ∠ 90.00°</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>1.2896 ∠ -90.00°</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>1.2896 ∠ -90.00°</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>2.1255 ∠ 90.00°</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>3.4151 ∠ 90.00°</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>3.4151 ∠ 90.00°</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Correntes Injetadas nos Barramentos</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Barra 1</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>13.3206 ∠ 90.00°</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>19.2450 ∠ 150.00°</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>19.2450 ∠ 30.00°</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>10.8552 ∠ 90.00°</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>8.3898 ∠ -90.00°</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>10.8552 ∠ 90.00°</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Correntes Injetadas nos Barramentos</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Barra 2</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>0.0000 ∠ 0.00°</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>0.0000 ∠ 0.00°</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>0.0000 ∠ 0.00°</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>0.0000 ∠ 0.00°</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>0.0000 ∠ 0.00°</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>0.0000 ∠ 0.00°</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Correntes Injetadas nos Barramentos</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Barra 3</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>0.0000 ∠ 0.00°</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>0.0000 ∠ 0.00°</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>0.0000 ∠ 0.00°</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>0.0000 ∠ 0.00°</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>0.0000 ∠ 0.00°</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>0.0000 ∠ 0.00°</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Correntes Injetadas nos Barramentos</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Barra 4</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
           <t>15.3960 ∠ -90.00°</t>
         </is>
       </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>15.3960 ∠ 150.00°</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>15.3960 ∠ 30.00°</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>0.0000 ∠ 0.00°</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>15.3960 ∠ -90.00°</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>0.0000 ∠ 0.00°</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H17"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Tipo</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Elemento / IF</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Fase A</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Fase B</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Fase C</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Seq. (0)</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Seq. (+)</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Seq. (-)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Correntes de Falta</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>25.3749 ∠ -90.00°</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>25.3749 ∠ -90.00°</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>25.3749 ∠ 150.00°</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>25.3749 ∠ 30.00°</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>25.3749 ∠ -90.00°</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Tensões nas Barras</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Barra 1</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>4.1698 ∠ 0.00°</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>4.1698 ∠ -120.00°</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>4.1698 ∠ 120.00°</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>0.0000 ∠ 0.00°</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>4.1698 ∠ 0.00°</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>0.0000 ∠ 0.00°</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Tensões nas Barras</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Barra 2</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>72.2971 ∠ 0.00°</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>72.2971 ∠ -120.00°</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>72.2971 ∠ 120.00°</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>0.0000 ∠ 0.00°</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>72.2971 ∠ 0.00°</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>0.0000 ∠ 0.00°</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Tensões nas Barras</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Barra 3</t>
+        </is>
+      </c>
       <c r="C5" t="inlineStr">
         <is>
+          <t>20.6563 ∠ 0.00°</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>20.6563 ∠ -120.00°</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>20.6563 ∠ 120.00°</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>0.0000 ∠ 0.00°</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>20.6563 ∠ 0.00°</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>0.0000 ∠ 0.00°</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Tensões nas Barras</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Barra 4</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>0.0000 ∠ 0.00°</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>0.0000 ∠ 0.00°</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>0.0000 ∠ 0.00°</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>0.0000 ∠ 0.00°</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>0.0000 ∠ 0.00°</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>0.0000 ∠ 0.00°</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Correntes de Contribuição</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Linha 2-3</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>0.4339 ∠ -90.00°</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>0.4339 ∠ 150.00°</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>0.4339 ∠ 30.00°</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>0.0000 ∠ 0.00°</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>0.4339 ∠ -90.00°</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>0.0000 ∠ 0.00°</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Correntes de Contribuição</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>G1</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>9.9789 ∠ -90.00°</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>9.9789 ∠ 150.00°</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>9.9789 ∠ 30.00°</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>0.0000 ∠ 0.00°</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>9.9789 ∠ -90.00°</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>0.0000 ∠ 0.00°</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Correntes de Contribuição</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>G4</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>15.3960 ∠ -90.00°</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
           <t>15.3960 ∠ 150.00°</t>
         </is>
       </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>15.3960 ∠ 30.00°</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>0.0000 ∠ 0.00°</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>15.3960 ∠ -90.00°</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>0.0000 ∠ 0.00°</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Correntes de Contribuição</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Trafo 1 (Primário)</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>9.9789 ∠ -90.00°</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>9.9789 ∠ 150.00°</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>9.9789 ∠ 30.00°</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>0.0000 ∠ 0.00°</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>9.9789 ∠ -90.00°</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>0.0000 ∠ 0.00°</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Correntes de Contribuição</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Trafo 1 (Secundário)</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>0.4339 ∠ -90.00°</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>0.4339 ∠ 150.00°</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>0.4339 ∠ 30.00°</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>0.0000 ∠ 0.00°</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>0.4339 ∠ -90.00°</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>0.0000 ∠ 0.00°</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Correntes de Contribuição</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Trafo 2 (Primário)</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>0.4339 ∠ -90.00°</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>0.4339 ∠ 150.00°</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>0.4339 ∠ 30.00°</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>0.0000 ∠ 0.00°</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>0.4339 ∠ -90.00°</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>0.0000 ∠ 0.00°</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Correntes de Contribuição</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Trafo 2 (Secundário)</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>9.9789 ∠ -90.00°</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>9.9789 ∠ 150.00°</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>9.9789 ∠ 30.00°</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>0.0000 ∠ 0.00°</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>9.9789 ∠ -90.00°</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>0.0000 ∠ 0.00°</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Correntes Injetadas nos Barramentos</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Barra 1</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>19.2450 ∠ -90.00°</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>19.2450 ∠ 150.00°</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>19.2450 ∠ 30.00°</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>0.0000 ∠ 0.00°</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>19.2450 ∠ -90.00°</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>0.0000 ∠ 0.00°</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Correntes Injetadas nos Barramentos</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Barra 2</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>0.0000 ∠ 0.00°</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>0.0000 ∠ 0.00°</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>0.0000 ∠ 0.00°</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>0.0000 ∠ 0.00°</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>0.0000 ∠ 0.00°</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>0.0000 ∠ 0.00°</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Correntes Injetadas nos Barramentos</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Barra 3</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>0.0000 ∠ 0.00°</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>0.0000 ∠ 0.00°</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>0.0000 ∠ 0.00°</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>0.0000 ∠ 0.00°</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>0.0000 ∠ 0.00°</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>0.0000 ∠ 0.00°</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Correntes Injetadas nos Barramentos</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Barra 4</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>9.9789 ∠ 90.00°</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>9.9789 ∠ -30.00°</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>9.9789 ∠ -150.00°</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>0.0000 ∠ 0.00°</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>9.9789 ∠ 90.00°</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>0.0000 ∠ 0.00°</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H17"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Tipo</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Elemento / IF</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Fase A</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Fase B</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Fase C</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Seq. (0)</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Seq. (+)</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Seq. (-)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Correntes de Falta</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>1.3984 ∠ 90.00°</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>0.0000 ∠ 0.00°</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>1.1888 ∠ 143.97°</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>1.1888 ∠ 36.03°</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>0.4661 ∠ 90.00°</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>0.7881 ∠ -90.00°</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>0.3220 ∠ 90.00°</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Tensões nas Barras</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Barra 1</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>7.4245 ∠ 0.00°</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>1.7932 ∠ -128.91°</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>1.7932 ∠ 128.91°</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>1.7240 ∠ 0.00°</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>3.6559 ∠ 0.00°</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>2.0447 ∠ 0.00°</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Tensões nas Barras</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Barra 2</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>173.3311 ∠ 0.00°</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>0.0000 ∠ 0.00°</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>0.0000 ∠ 0.00°</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>57.7770 ∠ 0.00°</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>57.7770 ∠ 0.00°</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>57.7770 ∠ 0.00°</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Tensões nas Barras</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Barra 3</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>163.1165 ∠ 0.00°</t>
+        </is>
+      </c>
       <c r="D5" t="inlineStr">
         <is>
+          <t>61.2575 ∠ -133.78°</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>61.2575 ∠ 133.78°</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>26.1184 ∠ 0.00°</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>94.0357 ∠ 0.00°</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>42.9624 ∠ 0.00°</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Tensões nas Barras</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Barra 4</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>7.1897 ∠ 0.00°</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>3.5438 ∠ -130.56°</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>3.5438 ∠ 130.56°</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>0.8603 ∠ 0.00°</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>4.7191 ∠ 0.00°</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>1.6103 ∠ 0.00°</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Correntes de Contribuição</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Linha 2-3</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>0.0472 ∠ 90.00°</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>0.4334 ∠ -30.98°</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>0.4334 ∠ -149.02°</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>0.1330 ∠ -90.00°</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>0.3046 ∠ 90.00°</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>0.1245 ∠ -90.00°</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Correntes de Contribuição</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>G1</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>1.0850 ∠ 90.00°</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>17.4341 ∠ 141.09°</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>17.4341 ∠ 38.91°</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>7.6620 ∠ 90.00°</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>11.1208 ∠ -90.00°</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>4.5438 ∠ 90.00°</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Correntes de Contribuição</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>G4</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>1.0850 ∠ -90.00°</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>9.9687 ∠ 149.02°</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>9.9687 ∠ 30.98°</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>3.0588 ∠ 90.00°</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>7.0065 ∠ -90.00°</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>2.8627 ∠ 90.00°</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Correntes de Contribuição</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Trafo 1 (Primário)</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>1.0850 ∠ 90.00°</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>17.4341 ∠ 141.09°</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>17.4341 ∠ 38.91°</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>7.6620 ∠ 90.00°</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>11.1208 ∠ -90.00°</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>4.5438 ∠ 90.00°</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Correntes de Contribuição</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Trafo 1 (Secundário)</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>0.0472 ∠ 90.00°</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>0.7580 ∠ 141.09°</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>0.7580 ∠ 38.91°</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>0.3331 ∠ 90.00°</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>0.4835 ∠ -90.00°</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>0.1976 ∠ 90.00°</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Correntes de Contribuição</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Trafo 2 (Primário)</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>0.0472 ∠ 90.00°</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>0.4334 ∠ -30.98°</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>0.4334 ∠ -149.02°</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>0.1330 ∠ -90.00°</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>0.3046 ∠ 90.00°</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>0.1245 ∠ -90.00°</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Correntes de Contribuição</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Trafo 2 (Secundário)</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>1.0850 ∠ 90.00°</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>9.9687 ∠ -30.98°</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>9.9687 ∠ -149.02°</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>3.0588 ∠ -90.00°</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>7.0065 ∠ 90.00°</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>2.8627 ∠ -90.00°</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Correntes Injetadas nos Barramentos</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Barra 1</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>19.2450 ∠ -90.00°</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>19.2450 ∠ 150.00°</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>19.2450 ∠ 30.00°</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>0.0000 ∠ 0.00°</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>19.2450 ∠ -90.00°</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>0.0000 ∠ 0.00°</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Correntes Injetadas nos Barramentos</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Barra 2</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>0.0000 ∠ 0.00°</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>1.1888 ∠ -36.03°</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>1.1888 ∠ -143.97°</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>0.4661 ∠ -90.00°</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>0.7881 ∠ 90.00°</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>0.3220 ∠ -90.00°</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Correntes Injetadas nos Barramentos</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Barra 3</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>0.0000 ∠ 0.00°</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>0.0000 ∠ 0.00°</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>0.0000 ∠ 0.00°</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>0.0000 ∠ 0.00°</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>0.0000 ∠ 0.00°</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>0.0000 ∠ 0.00°</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Correntes Injetadas nos Barramentos</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Barra 4</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>15.3960 ∠ -90.00°</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>15.3960 ∠ 150.00°</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
           <t>15.3960 ∠ 30.00°</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>0.0000 ∠ 0.00°</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>0.0000 ∠ 0.00°</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
         <is>
           <t>15.3960 ∠ -90.00°</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="H17" t="inlineStr">
         <is>
           <t>0.0000 ∠ 0.00°</t>
         </is>

--- a/resultados.xlsx
+++ b/resultados.xlsx
@@ -1,17 +1,19 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Ybarra (+) (-)" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Zbarra (+) (-)" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Ybarra (0)" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Zbarra (0)" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Curto Monofásico - Barra 4" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ybarra (+) (-)" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Zbarra (+) (-)" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ybarra (0)" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Zbarra (0)" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Curto Monofásico - Barra 4" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Curto Bifásico-Terra - Barra 1" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Curto Trifásico - Barra 3" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1661,4 +1663,1460 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H17"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Tipo</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Elemento / IF</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Fase A</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Fase B</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Fase C</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Seq. (0)</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Seq. (+)</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Seq. (-)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Correntes de Falta</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>57.7860 ∠ 90.00°</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>0.0000 ∠ 0.00°</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>37.7640 ∠ 130.08°</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>37.7640 ∠ 49.92°</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>19.2620 ∠ 90.00°</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>23.6704 ∠ -90.00°</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>4.4084 ∠ 90.00°</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Tensões nas Barras</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Barra 1</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>4.0790 ∠ 0.00°</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>0.0000 ∠ 0.00°</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>0.0000 ∠ 0.00°</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>1.3597 ∠ 0.00°</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>1.3597 ∠ 0.00°</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>1.3597 ∠ 0.00°</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Tensões nas Barras</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Barra 2</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>67.3958 ∠ -8.92°</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>67.3958 ∠ -171.08°</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>20.8982 ∠ 90.00°</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>0.0000 ∠ 0.00°</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>48.8895 ∠ -30.00°</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>27.9914 ∠ 30.00°</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Tensões nas Barras</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Barra 3</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>99.4808 ∠ -19.56°</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>99.4808 ∠ -160.44°</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>66.6130 ∠ 90.00°</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>0.0000 ∠ 0.00°</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>87.4271 ∠ -30.00°</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>20.8141 ∠ 30.00°</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Tensões nas Barras</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Barra 4</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>4.9082 ∠ -22.09°</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>4.9082 ∠ -157.91°</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>3.6913 ∠ 90.00°</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>0.0000 ∠ 0.00°</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>4.4714 ∠ -30.00°</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>0.7801 ∠ 30.00°</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Correntes de Contribuição</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Linha 2-3</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>0.2982 ∠ 49.92°</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>0.2982 ∠ -49.92°</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>0.3841 ∠ 180.00°</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>0.0000 ∠ 0.00°</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>0.3238 ∠ 60.00°</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>0.0603 ∠ -60.00°</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Correntes de Contribuição</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>G1</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>7.1591 ∠ -90.00°</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>20.9200 ∠ 142.81°</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>20.9200 ∠ 37.19°</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>6.0430 ∠ 90.00°</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>16.2235 ∠ -90.00°</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>3.0215 ∠ 90.00°</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Correntes de Contribuição</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>G4</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>6.8594 ∠ -130.08°</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>6.8594 ∠ 130.08°</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>8.8338 ∠ -0.00°</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>0.0000 ∠ 0.00°</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>7.4469 ∠ -120.00°</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>1.3869 ∠ 120.00°</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Correntes de Contribuição</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Trafo 1 (Primário)</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>6.0599 ∠ 90.00°</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>8.2285 ∠ -21.61°</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>8.2285 ∠ -158.39°</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>0.0000 ∠ 0.00°</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>7.4469 ∠ 90.00°</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>1.3869 ∠ -90.00°</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Correntes de Contribuição</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Trafo 1 (Secundário)</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>0.2982 ∠ 49.92°</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>0.2982 ∠ -49.92°</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>0.3841 ∠ 180.00°</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>0.0000 ∠ 0.00°</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>0.3238 ∠ 60.00°</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>0.0603 ∠ -60.00°</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Correntes de Contribuição</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Trafo 2 (Primário)</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>0.2982 ∠ 49.92°</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>0.2982 ∠ -49.92°</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>0.3841 ∠ 180.00°</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>0.0000 ∠ 0.00°</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>0.3238 ∠ 60.00°</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>0.0603 ∠ -60.00°</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Correntes de Contribuição</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Trafo 2 (Secundário)</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>6.8594 ∠ 49.92°</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>6.8594 ∠ -49.92°</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>8.8338 ∠ 180.00°</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>0.0000 ∠ 0.00°</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>7.4469 ∠ 60.00°</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>1.3869 ∠ -60.00°</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Correntes Injetadas nos Barramentos</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Barra 1</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>19.2450 ∠ -90.00°</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>20.7335 ∠ -68.35°</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>20.7335 ∠ -111.65°</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>19.2620 ∠ -90.00°</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>4.4254 ∠ 90.00°</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>4.4084 ∠ -90.00°</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Correntes Injetadas nos Barramentos</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Barra 2</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>0.0000 ∠ 0.00°</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>0.0000 ∠ 0.00°</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>0.0000 ∠ 0.00°</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>0.0000 ∠ 0.00°</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>0.0000 ∠ 0.00°</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>0.0000 ∠ 0.00°</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Correntes Injetadas nos Barramentos</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Barra 3</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>0.0000 ∠ 0.00°</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>0.0000 ∠ 0.00°</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>0.0000 ∠ 0.00°</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>0.0000 ∠ 0.00°</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>0.0000 ∠ 0.00°</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>0.0000 ∠ 0.00°</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Correntes Injetadas nos Barramentos</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Barra 4</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>15.3960 ∠ -90.00°</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>15.3960 ∠ 150.00°</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>15.3960 ∠ 30.00°</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>0.0000 ∠ 0.00°</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>15.3960 ∠ -90.00°</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>0.0000 ∠ 0.00°</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H17"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Tipo</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Elemento / IF</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Fase A</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Fase B</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Fase C</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Seq. (0)</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Seq. (+)</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Seq. (-)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Correntes de Falta</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>1.0611 ∠ -90.00°</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>1.0611 ∠ -90.00°</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>1.0611 ∠ 150.00°</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>1.0611 ∠ 30.00°</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>1.0611 ∠ -90.00°</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Tensões nas Barras</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Barra 1</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>3.6502 ∠ 30.00°</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>3.6502 ∠ -90.00°</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>3.6502 ∠ 150.00°</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>0.0000 ∠ 0.00°</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>3.6502 ∠ 30.00°</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>0.0000 ∠ 0.00°</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Tensões nas Barras</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Barra 2</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>57.6157 ∠ 0.00°</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>57.6157 ∠ -120.00°</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>57.6157 ∠ 120.00°</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>0.0000 ∠ 0.00°</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>57.6157 ∠ 0.00°</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>0.0000 ∠ 0.00°</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Tensões nas Barras</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Barra 3</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>0.0000 ∠ 0.00°</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>0.0000 ∠ 0.00°</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>0.0000 ∠ 0.00°</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>0.0000 ∠ 0.00°</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>0.0000 ∠ 0.00°</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>0.0000 ∠ 0.00°</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Tensões nas Barras</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Barra 4</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>1.1945 ∠ 0.00°</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>1.1945 ∠ -120.00°</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>1.1945 ∠ 120.00°</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>0.0000 ∠ 0.00°</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>1.1945 ∠ 0.00°</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>0.0000 ∠ 0.00°</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Correntes de Contribuição</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Linha 2-3</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>0.4841 ∠ -90.00°</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>0.4841 ∠ 150.00°</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>0.4841 ∠ 30.00°</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>0.0000 ∠ 0.00°</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>0.4841 ∠ -90.00°</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>0.0000 ∠ 0.00°</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Correntes de Contribuição</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>G1</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>11.1335 ∠ -60.00°</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>11.1335 ∠ 180.00°</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>11.1335 ∠ 60.00°</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>0.0000 ∠ 0.00°</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>11.1335 ∠ -60.00°</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>0.0000 ∠ 0.00°</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Correntes de Contribuição</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>G4</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>13.2724 ∠ -90.00°</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>13.2724 ∠ 150.00°</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>13.2724 ∠ 30.00°</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>0.0000 ∠ 0.00°</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>13.2724 ∠ -90.00°</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>0.0000 ∠ 0.00°</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Correntes de Contribuição</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Trafo 1 (Primário)</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>11.1335 ∠ -60.00°</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>11.1335 ∠ 180.00°</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>11.1335 ∠ 60.00°</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>0.0000 ∠ 0.00°</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>11.1335 ∠ -60.00°</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>0.0000 ∠ 0.00°</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Correntes de Contribuição</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Trafo 1 (Secundário)</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>0.4841 ∠ -90.00°</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>0.4841 ∠ 150.00°</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>0.4841 ∠ 30.00°</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>0.0000 ∠ 0.00°</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>0.4841 ∠ -90.00°</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>0.0000 ∠ 0.00°</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Correntes de Contribuição</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Trafo 2 (Primário)</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>0.5771 ∠ 90.00°</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>0.5771 ∠ -30.00°</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>0.5771 ∠ -150.00°</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>0.0000 ∠ 0.00°</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>0.5771 ∠ 90.00°</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>0.0000 ∠ 0.00°</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Correntes de Contribuição</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Trafo 2 (Secundário)</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>13.2724 ∠ 90.00°</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>13.2724 ∠ -30.00°</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>13.2724 ∠ -150.00°</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>0.0000 ∠ 0.00°</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>13.2724 ∠ 90.00°</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>0.0000 ∠ 0.00°</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Correntes Injetadas nos Barramentos</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Barra 1</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>19.2450 ∠ -90.00°</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>19.2450 ∠ 150.00°</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>19.2450 ∠ 30.00°</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>0.0000 ∠ 0.00°</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>19.2450 ∠ -90.00°</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>0.0000 ∠ 0.00°</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Correntes Injetadas nos Barramentos</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Barra 2</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>0.0000 ∠ 0.00°</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>0.0000 ∠ 0.00°</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>0.0000 ∠ 0.00°</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>0.0000 ∠ 0.00°</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>0.0000 ∠ 0.00°</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>0.0000 ∠ 0.00°</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Correntes Injetadas nos Barramentos</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Barra 3</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>1.0611 ∠ 90.00°</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>1.0611 ∠ -30.00°</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>1.0611 ∠ -150.00°</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>0.0000 ∠ 0.00°</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>1.0611 ∠ 90.00°</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>0.0000 ∠ 0.00°</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Correntes Injetadas nos Barramentos</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Barra 4</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>15.3960 ∠ -90.00°</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>15.3960 ∠ 150.00°</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>15.3960 ∠ 30.00°</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>0.0000 ∠ 0.00°</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>15.3960 ∠ -90.00°</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>0.0000 ∠ 0.00°</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/resultados.xlsx
+++ b/resultados.xlsx
@@ -13,7 +13,6 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Zbarra (0)" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Curto Monofásico - Barra 4" sheetId="5" state="visible" r:id="rId5"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Curto Bifásico-Terra - Barra 1" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Curto Trifásico - Barra 3" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -2391,732 +2390,4 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:H17"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Tipo</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Elemento / IF</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Fase A</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>Fase B</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>Fase C</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>Seq. (0)</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>Seq. (+)</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>Seq. (-)</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Correntes de Falta</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>1.0611 ∠ -90.00°</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>1.0611 ∠ -90.00°</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>1.0611 ∠ 150.00°</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>1.0611 ∠ 30.00°</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>1.0611 ∠ -90.00°</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Tensões nas Barras</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Barra 1</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>3.6502 ∠ 30.00°</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>3.6502 ∠ -90.00°</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>3.6502 ∠ 150.00°</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>0.0000 ∠ 0.00°</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>3.6502 ∠ 30.00°</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>0.0000 ∠ 0.00°</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Tensões nas Barras</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Barra 2</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>57.6157 ∠ 0.00°</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>57.6157 ∠ -120.00°</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>57.6157 ∠ 120.00°</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>0.0000 ∠ 0.00°</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>57.6157 ∠ 0.00°</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>0.0000 ∠ 0.00°</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Tensões nas Barras</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Barra 3</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>0.0000 ∠ 0.00°</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>0.0000 ∠ 0.00°</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>0.0000 ∠ 0.00°</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>0.0000 ∠ 0.00°</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>0.0000 ∠ 0.00°</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>0.0000 ∠ 0.00°</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Tensões nas Barras</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Barra 4</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>1.1945 ∠ 0.00°</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>1.1945 ∠ -120.00°</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>1.1945 ∠ 120.00°</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>0.0000 ∠ 0.00°</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>1.1945 ∠ 0.00°</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>0.0000 ∠ 0.00°</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Correntes de Contribuição</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Linha 2-3</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>0.4841 ∠ -90.00°</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>0.4841 ∠ 150.00°</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>0.4841 ∠ 30.00°</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>0.0000 ∠ 0.00°</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>0.4841 ∠ -90.00°</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>0.0000 ∠ 0.00°</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Correntes de Contribuição</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>G1</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>11.1335 ∠ -60.00°</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>11.1335 ∠ 180.00°</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>11.1335 ∠ 60.00°</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>0.0000 ∠ 0.00°</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>11.1335 ∠ -60.00°</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>0.0000 ∠ 0.00°</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Correntes de Contribuição</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>G4</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>13.2724 ∠ -90.00°</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>13.2724 ∠ 150.00°</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>13.2724 ∠ 30.00°</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>0.0000 ∠ 0.00°</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>13.2724 ∠ -90.00°</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>0.0000 ∠ 0.00°</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Correntes de Contribuição</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>Trafo 1 (Primário)</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>11.1335 ∠ -60.00°</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>11.1335 ∠ 180.00°</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>11.1335 ∠ 60.00°</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>0.0000 ∠ 0.00°</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>11.1335 ∠ -60.00°</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>0.0000 ∠ 0.00°</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Correntes de Contribuição</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>Trafo 1 (Secundário)</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>0.4841 ∠ -90.00°</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>0.4841 ∠ 150.00°</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>0.4841 ∠ 30.00°</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>0.0000 ∠ 0.00°</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>0.4841 ∠ -90.00°</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>0.0000 ∠ 0.00°</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Correntes de Contribuição</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>Trafo 2 (Primário)</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>0.5771 ∠ 90.00°</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>0.5771 ∠ -30.00°</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>0.5771 ∠ -150.00°</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>0.0000 ∠ 0.00°</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>0.5771 ∠ 90.00°</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>0.0000 ∠ 0.00°</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>Correntes de Contribuição</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>Trafo 2 (Secundário)</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>13.2724 ∠ 90.00°</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>13.2724 ∠ -30.00°</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>13.2724 ∠ -150.00°</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>0.0000 ∠ 0.00°</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>13.2724 ∠ 90.00°</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>0.0000 ∠ 0.00°</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Correntes Injetadas nos Barramentos</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>Barra 1</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>19.2450 ∠ -90.00°</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>19.2450 ∠ 150.00°</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>19.2450 ∠ 30.00°</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>0.0000 ∠ 0.00°</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>19.2450 ∠ -90.00°</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>0.0000 ∠ 0.00°</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>Correntes Injetadas nos Barramentos</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>Barra 2</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>0.0000 ∠ 0.00°</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>0.0000 ∠ 0.00°</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>0.0000 ∠ 0.00°</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>0.0000 ∠ 0.00°</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>0.0000 ∠ 0.00°</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>0.0000 ∠ 0.00°</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>Correntes Injetadas nos Barramentos</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>Barra 3</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>1.0611 ∠ 90.00°</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>1.0611 ∠ -30.00°</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>1.0611 ∠ -150.00°</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>0.0000 ∠ 0.00°</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>1.0611 ∠ 90.00°</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>0.0000 ∠ 0.00°</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>Correntes Injetadas nos Barramentos</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>Barra 4</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>15.3960 ∠ -90.00°</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>15.3960 ∠ 150.00°</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>15.3960 ∠ 30.00°</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>0.0000 ∠ 0.00°</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>15.3960 ∠ -90.00°</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>0.0000 ∠ 0.00°</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
 </file>